--- a/习题册excel.xlsx
+++ b/习题册excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\34406\Documents\Obsidian Vault\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29CA410-4C04-43AC-B50C-669E5973BCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E458576-A84E-47EC-B472-1B2220B2F11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -988,6 +988,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -995,25 +1006,1414 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="258">
+  <dxfs count="231">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF006100"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1046,6 +2446,34 @@
       <font>
         <b/>
         <sz val="10.5"/>
+        <color rgb="FF9C0006"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF9C6500"/>
+        <name val="微软雅黑"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF006100"/>
         <name val="微软雅黑"/>
       </font>
@@ -1184,39 +2612,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <sz val="10.5"/>
         <color rgb="FF9C0006"/>
@@ -1301,6 +2696,336 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <sz val="10.5"/>
         <color rgb="FF9C0006"/>
@@ -1385,6 +3110,336 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <sz val="10.5"/>
         <color rgb="FF9C0006"/>
@@ -1427,10 +3482,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <sz val="10.5"/>
         <color rgb="FF9C0006"/>
-        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -1441,10 +3493,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF9C6500"/>
-        <name val="微软雅黑"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -1455,10 +3504,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <sz val="10.5"/>
         <color rgb="FF006100"/>
-        <name val="微软雅黑"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -1469,6 +3515,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1502,17 +3559,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1530,2349 +3576,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4055,7 +3758,7 @@
                   <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>317</c:v>
+                  <c:v>361</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>593</c:v>
@@ -4137,7 +3840,7 @@
                   <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>246</c:v>
+                  <c:v>274</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>438</c:v>
@@ -4967,10 +4670,10 @@
                   <c:v>0.75757575757575757</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.63636363636363635</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.63636363636363635</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.63636363636363635</c:v>
@@ -7018,7 +6721,7 @@
                   <c:v>0.82352941176470584</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.77602523659305989</c:v>
+                  <c:v>0.75900277008310246</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.73861720067453629</c:v>
@@ -7196,7 +6899,7 @@
                   <c:v>0.14084507042253522</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5555555555555556</c:v>
+                  <c:v>1.6666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1.25</c:v>
@@ -7381,7 +7084,7 @@
                   <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>910</c:v>
+                  <c:v>954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7445,7 +7148,7 @@
                   <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>684</c:v>
+                  <c:v>712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7638,7 +7341,7 @@
                   <c:v>0.82352941176470584</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.75164835164835164</c:v>
+                  <c:v>0.74633123689727465</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7702,7 +7405,7 @@
                   <c:v>0.14084507042253522</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6454545454545455</c:v>
+                  <c:v>0.66363636363636369</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9520,14 +9223,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -9550,7 +9253,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="18"/>
@@ -9610,7 +9313,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="18"/>
@@ -9625,23 +9328,23 @@
       </c>
       <c r="B9" s="3">
         <f>SUMPRODUCT((王道操作系统!C5:C50&gt;0)*1)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3">
         <f>王道操作系统!C30</f>
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="D9" s="3">
         <f>王道操作系统!D30</f>
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="E9" s="3">
         <f>IF(C9&gt;0, D9/C9,"")</f>
-        <v>0.77602523659305989</v>
+        <v>0.75900277008310246</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9&gt;0, B9/18, "")</f>
-        <v>1.5555555555555556</v>
+        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -9725,23 +9428,23 @@
       </c>
       <c r="B13" s="5">
         <f>SUM(B9:B12)</f>
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" s="5">
         <f>SUM(C9:C12)</f>
-        <v>910</v>
+        <v>954</v>
       </c>
       <c r="D13" s="5">
         <f>SUM(D9:D12)</f>
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="E13" s="5">
         <f>IF(C13&gt;0, D13/C13, "")</f>
-        <v>0.75164835164835164</v>
+        <v>0.74633123689727465</v>
       </c>
       <c r="F13" s="5">
         <f>IF(B13&gt;0, B13/110, "")</f>
-        <v>0.6454545454545455</v>
+        <v>0.66363636363636369</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -9750,23 +9453,23 @@
       </c>
       <c r="B15" s="8">
         <f>SUM(B6,B13)</f>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" s="8">
         <f>SUM(C6,C13)</f>
-        <v>1114</v>
+        <v>1158</v>
       </c>
       <c r="D15" s="8">
         <f>SUM(D6,D13)</f>
-        <v>852</v>
+        <v>880</v>
       </c>
       <c r="E15" s="8">
         <f>IF(C15&gt;0, D15/C15, "")</f>
-        <v>0.76481149012567329</v>
+        <v>0.75993091537132984</v>
       </c>
       <c r="F15" s="8">
         <f>IF(B15&gt;0, B15/181, "")</f>
-        <v>0.44751381215469616</v>
+        <v>0.4585635359116022</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -9813,19 +9516,19 @@
       </c>
       <c r="B22">
         <f t="shared" ref="B22:E25" si="0">C9</f>
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>0.77602523659305989</v>
+        <v>0.75900277008310246</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
-        <v>1.5555555555555556</v>
+        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -9935,19 +9638,19 @@
       </c>
       <c r="B32">
         <f>C13</f>
-        <v>910</v>
+        <v>954</v>
       </c>
       <c r="C32">
         <f>D13</f>
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="D32">
         <f>E13</f>
-        <v>0.75164835164835164</v>
+        <v>0.74633123689727465</v>
       </c>
       <c r="E32">
         <f>F13</f>
-        <v>0.6454545454545455</v>
+        <v>0.66363636363636369</v>
       </c>
     </row>
   </sheetData>
@@ -9958,62 +9661,62 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="E5:E6">
-    <cfRule type="cellIs" dxfId="257" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="230" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="229" priority="2" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="228" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E13">
-    <cfRule type="cellIs" dxfId="254" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="227" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="226" priority="8" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="225" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="cellIs" dxfId="251" priority="38" operator="between">
+    <cfRule type="cellIs" dxfId="224" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="223" priority="38" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="39" operator="lessThan">
+    <cfRule type="cellIs" dxfId="222" priority="39" operator="lessThan">
       <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="37" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="248" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="221" priority="4" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="247" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="220" priority="5" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="246" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="219" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="245" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="218" priority="10" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="244" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="217" priority="11" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="216" priority="12" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10037,13 +9740,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -10063,7 +9766,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="18"/>
@@ -10085,13 +9788,13 @@
         <v>30</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="22">
+      <c r="C6" s="15">
         <v>10</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="15">
         <v>10</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="16">
         <f t="shared" ref="E6:E16" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
         <v>1</v>
       </c>
@@ -10101,13 +9804,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="22">
+      <c r="C7" s="15">
         <v>23</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="15">
         <v>20</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="16">
         <f t="shared" si="0"/>
         <v>0.86956521739130432</v>
       </c>
@@ -10117,13 +9820,13 @@
         <v>32</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="22">
+      <c r="C8" s="15">
         <v>12</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="15">
         <v>11</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="16">
         <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
@@ -10133,13 +9836,13 @@
         <v>33</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="22">
+      <c r="C9" s="15">
         <v>15</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="15">
         <v>12</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="16">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
@@ -10149,13 +9852,13 @@
         <v>34</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="22">
+      <c r="C10" s="15">
         <v>18</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="15">
         <v>15</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="16">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
@@ -10165,13 +9868,13 @@
         <v>35</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="22">
+      <c r="C11" s="15">
         <v>24</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="15">
         <v>18</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="16">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -10181,13 +9884,13 @@
         <v>36</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="22">
+      <c r="C12" s="15">
         <v>22</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="15">
         <v>20</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="16">
         <f t="shared" si="0"/>
         <v>0.90909090909090906</v>
       </c>
@@ -10197,9 +9900,9 @@
         <v>37</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23" t="str">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -10209,13 +9912,13 @@
         <v>38</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="22">
+      <c r="C14" s="15">
         <v>25</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="15">
         <v>24</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="16">
         <f t="shared" si="0"/>
         <v>0.96</v>
       </c>
@@ -10225,13 +9928,13 @@
         <v>39</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="22">
+      <c r="C15" s="15">
         <v>36</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="15">
         <v>28</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="16">
         <f t="shared" si="0"/>
         <v>0.77777777777777779</v>
       </c>
@@ -10241,13 +9944,13 @@
         <v>40</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="22">
+      <c r="C16" s="15">
         <v>19</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="15">
         <v>10</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="16">
         <f t="shared" si="0"/>
         <v>0.52631578947368418</v>
       </c>
@@ -10260,7 +9963,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="str">
-        <f t="shared" ref="E6:E24" si="1">IF(AND(C17&lt;&gt;"",D17&lt;&gt;""),D17/C17,"")</f>
+        <f t="shared" ref="E17:E24" si="1">IF(AND(C17&lt;&gt;"",D17&lt;&gt;""),D17/C17,"")</f>
         <v/>
       </c>
     </row>
@@ -10529,7 +10232,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="23" t="s">
         <v>64</v>
       </c>
       <c r="B41" s="18"/>
@@ -10781,7 +10484,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A63" s="21" t="s">
+      <c r="A63" s="23" t="s">
         <v>66</v>
       </c>
       <c r="B63" s="18"/>
@@ -11024,7 +10727,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A84" s="21" t="s">
+      <c r="A84" s="23" t="s">
         <v>83</v>
       </c>
       <c r="B84" s="18"/>
@@ -11858,135 +11561,135 @@
     <mergeCell ref="A84:E84"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <conditionalFormatting sqref="E17:E24">
-    <cfRule type="cellIs" dxfId="242" priority="4" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="E6:E16">
+    <cfRule type="cellIs" dxfId="215" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="214" priority="2" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="213" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E24">
+    <cfRule type="cellIs" dxfId="212" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="211" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="210" priority="6" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26:E31">
-    <cfRule type="cellIs" dxfId="239" priority="61" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="209" priority="61" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="62" operator="between">
+    <cfRule type="cellIs" dxfId="208" priority="62" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="207" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E38">
-    <cfRule type="cellIs" dxfId="236" priority="79" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="206" priority="79" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="80" operator="between">
+    <cfRule type="cellIs" dxfId="205" priority="80" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="81" operator="lessThan">
+    <cfRule type="cellIs" dxfId="204" priority="81" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="233" priority="211" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="203" priority="211" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="212" operator="between">
+    <cfRule type="cellIs" dxfId="202" priority="212" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="213" operator="lessThan">
+    <cfRule type="cellIs" dxfId="201" priority="213" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43:E60">
-    <cfRule type="cellIs" dxfId="230" priority="94" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="200" priority="94" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="229" priority="95" operator="between">
+    <cfRule type="cellIs" dxfId="199" priority="95" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="96" operator="lessThan">
+    <cfRule type="cellIs" dxfId="198" priority="96" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64:E73">
-    <cfRule type="cellIs" dxfId="227" priority="148" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="197" priority="148" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="226" priority="149" operator="between">
+    <cfRule type="cellIs" dxfId="196" priority="149" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="225" priority="150" operator="lessThan">
+    <cfRule type="cellIs" dxfId="195" priority="150" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E76:E83">
-    <cfRule type="cellIs" dxfId="224" priority="175" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="194" priority="175" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="223" priority="176" operator="between">
+    <cfRule type="cellIs" dxfId="193" priority="176" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="177" operator="lessThan">
+    <cfRule type="cellIs" dxfId="192" priority="177" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85:E88">
-    <cfRule type="cellIs" dxfId="221" priority="199" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="191" priority="199" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="200" operator="between">
+    <cfRule type="cellIs" dxfId="190" priority="200" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="219" priority="201" operator="lessThan">
+    <cfRule type="cellIs" dxfId="189" priority="201" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E91">
-    <cfRule type="cellIs" dxfId="218" priority="222" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="217" priority="220" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="188" priority="220" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="221" operator="between">
+    <cfRule type="cellIs" dxfId="187" priority="221" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="186" priority="222" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E94">
-    <cfRule type="cellIs" dxfId="215" priority="217" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="185" priority="217" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="214" priority="218" operator="between">
+    <cfRule type="cellIs" dxfId="184" priority="218" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="219" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E16">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="183" priority="219" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12011,20 +11714,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="22" t="s">
         <v>98</v>
       </c>
       <c r="B3" s="18"/>
@@ -12032,7 +11735,7 @@
       <c r="D3" s="18"/>
       <c r="E3" s="19"/>
       <c r="F3" s="13"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="17" t="s">
         <v>99</v>
       </c>
       <c r="H3" s="18"/>
@@ -12082,16 +11785,16 @@
       <c r="A6" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="15">
         <v>530</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="15">
         <v>11</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="15">
         <v>10</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="16">
         <f t="shared" ref="E6:E11" si="0">IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
         <v>0.90909090909090906</v>
       </c>
@@ -12107,16 +11810,16 @@
       <c r="A7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="15">
         <v>530</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="15">
         <v>20</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="15">
         <v>14</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="16">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
@@ -12132,16 +11835,16 @@
       <c r="A8" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="15">
         <v>530</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="15">
         <v>33</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="15">
         <v>25</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="16">
         <f t="shared" si="0"/>
         <v>0.75757575757575757</v>
       </c>
@@ -12157,14 +11860,18 @@
       <c r="A9" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="15">
         <v>531</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="str">
+      <c r="C9" s="15">
+        <v>22</v>
+      </c>
+      <c r="D9" s="15">
+        <v>14</v>
+      </c>
+      <c r="E9" s="16">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0.63636363636363635</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="3"/>
@@ -12178,14 +11885,18 @@
       <c r="A10" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="15">
         <v>531</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23" t="str">
+      <c r="C10" s="15">
+        <v>22</v>
+      </c>
+      <c r="D10" s="15">
+        <v>14</v>
+      </c>
+      <c r="E10" s="16">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0.63636363636363635</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="3"/>
@@ -12199,16 +11910,16 @@
       <c r="A11" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="15">
         <v>531</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="15">
         <v>22</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="15">
         <v>14</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="16">
         <f t="shared" si="0"/>
         <v>0.63636363636363635</v>
       </c>
@@ -12237,16 +11948,16 @@
       <c r="A13" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="15">
         <v>601</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="15">
         <v>73</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="15">
         <v>53</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="16">
         <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;""),D13/C13,"")</f>
         <v>0.72602739726027399</v>
       </c>
@@ -12262,16 +11973,16 @@
       <c r="A14" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="15">
         <v>602</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="15">
         <v>57</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="15">
         <v>46</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="16">
         <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;""),D14/C14,"")</f>
         <v>0.80701754385964908</v>
       </c>
@@ -12287,16 +11998,16 @@
       <c r="A15" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="15">
         <v>606</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="15">
         <v>56</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="15">
         <v>46</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="16">
         <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;""),D15/C15,"")</f>
         <v>0.8214285714285714</v>
       </c>
@@ -12312,16 +12023,16 @@
       <c r="A16" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="15">
         <v>607</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="15">
         <v>45</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="15">
         <v>38</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="16">
         <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;""),D16/C16,"")</f>
         <v>0.84444444444444444</v>
       </c>
@@ -12531,15 +12242,15 @@
       <c r="B28" s="12"/>
       <c r="C28" s="12">
         <f>SUM(C5:C27)</f>
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="D28" s="12">
         <f>SUM(D5:D27)</f>
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="E28" s="12">
         <f>IF(C28&gt;0, D28/C28,"")</f>
-        <v>0.77602523659305989</v>
+        <v>0.75900277008310246</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12">
@@ -12562,15 +12273,15 @@
       <c r="B30" s="8"/>
       <c r="C30" s="8">
         <f>C28+G28</f>
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="D30" s="8">
         <f>D28+H28</f>
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="E30" s="8">
         <f>IF(C30&gt;0, D30/C30,"")</f>
-        <v>0.77602523659305989</v>
+        <v>0.75900277008310246</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
@@ -12631,9 +12342,9 @@
       <c r="A37" t="s">
         <v>107</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B37">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.63636363636363635</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="3"/>
@@ -12644,9 +12355,9 @@
       <c r="A38" t="s">
         <v>108</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B38">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.63636363636363635</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="3"/>
@@ -12829,147 +12540,147 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="206" priority="39" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="37" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="E6:E11">
+    <cfRule type="cellIs" dxfId="182" priority="4" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="38" operator="between">
+    <cfRule type="cellIs" dxfId="181" priority="5" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="180" priority="6" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E16">
+    <cfRule type="cellIs" dxfId="179" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="178" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="177" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18:E19">
+    <cfRule type="cellIs" dxfId="176" priority="37" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="175" priority="38" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="174" priority="39" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E23">
-    <cfRule type="cellIs" dxfId="203" priority="43" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="173" priority="43" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="44" operator="between">
+    <cfRule type="cellIs" dxfId="172" priority="44" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="45" operator="lessThan">
+    <cfRule type="cellIs" dxfId="171" priority="45" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:E28">
-    <cfRule type="cellIs" dxfId="200" priority="52" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="170" priority="52" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="53" operator="between">
+    <cfRule type="cellIs" dxfId="169" priority="53" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="54" operator="lessThan">
+    <cfRule type="cellIs" dxfId="168" priority="54" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="197" priority="64" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="167" priority="64" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="65" operator="between">
+    <cfRule type="cellIs" dxfId="166" priority="65" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="66" operator="lessThan">
+    <cfRule type="cellIs" dxfId="165" priority="66" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I11">
-    <cfRule type="cellIs" dxfId="194" priority="67" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="164" priority="67" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="68" operator="between">
+    <cfRule type="cellIs" dxfId="163" priority="68" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="69" operator="lessThan">
+    <cfRule type="cellIs" dxfId="162" priority="69" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="191" priority="85" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="161" priority="85" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="86" operator="between">
+    <cfRule type="cellIs" dxfId="160" priority="86" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="87" operator="lessThan">
+    <cfRule type="cellIs" dxfId="159" priority="87" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="188" priority="97" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="158" priority="97" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="98" operator="between">
+    <cfRule type="cellIs" dxfId="157" priority="98" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="156" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I23">
-    <cfRule type="cellIs" dxfId="185" priority="103" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="155" priority="103" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="104" operator="between">
+    <cfRule type="cellIs" dxfId="154" priority="104" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="153" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:I28">
-    <cfRule type="cellIs" dxfId="182" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="112" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="152" priority="112" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="113" operator="between">
+    <cfRule type="cellIs" dxfId="151" priority="113" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="150" priority="114" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30">
-    <cfRule type="cellIs" dxfId="179" priority="126" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="124" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="149" priority="124" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="125" operator="between">
+    <cfRule type="cellIs" dxfId="148" priority="125" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E11">
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="6" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="147" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12994,20 +12705,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="22" t="s">
         <v>98</v>
       </c>
       <c r="B3" s="18"/>
@@ -13015,7 +12726,7 @@
       <c r="D3" s="18"/>
       <c r="E3" s="19"/>
       <c r="F3" s="13"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="17" t="s">
         <v>99</v>
       </c>
       <c r="H3" s="18"/>
@@ -13065,16 +12776,16 @@
       <c r="A6" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="15">
         <v>507</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="15">
         <v>1</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="15">
         <v>1</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="16">
         <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;""),D6/C6,"")</f>
         <v>1</v>
       </c>
@@ -13090,16 +12801,16 @@
       <c r="A7" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="15">
         <v>507</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="15">
         <v>14</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="15">
         <v>13</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="16">
         <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;""),D7/C7,"")</f>
         <v>0.9285714285714286</v>
       </c>
@@ -13115,16 +12826,16 @@
       <c r="A8" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="15">
         <v>508</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="15">
         <v>20</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="15">
         <v>12</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="16">
         <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;""),D8/C8,"")</f>
         <v>0.6</v>
       </c>
@@ -13153,16 +12864,16 @@
       <c r="A10" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="15">
         <v>509</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="15">
         <v>34</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="15">
         <v>25</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="16">
         <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;""),D10/C10,"")</f>
         <v>0.73529411764705888</v>
       </c>
@@ -13178,16 +12889,16 @@
       <c r="A11" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="15">
         <v>510</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="15">
         <v>35</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="15">
         <v>25</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="16">
         <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;""),D11/C11,"")</f>
         <v>0.7142857142857143</v>
       </c>
@@ -13203,16 +12914,16 @@
       <c r="A12" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="15">
         <v>512</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="15">
         <v>45</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="15">
         <v>37</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="16">
         <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;""),D12/C12,"")</f>
         <v>0.82222222222222219</v>
       </c>
@@ -13241,16 +12952,16 @@
       <c r="A14" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="15">
         <v>513</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="15">
         <v>11</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="15">
         <v>10</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="16">
         <f t="shared" ref="E14:E19" si="0">IF(AND(C14&lt;&gt;"",D14&lt;&gt;""),D14/C14,"")</f>
         <v>0.90909090909090906</v>
       </c>
@@ -13266,16 +12977,16 @@
       <c r="A15" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="15">
         <v>514</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="15">
         <v>37</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="15">
         <v>30</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="16">
         <f t="shared" si="0"/>
         <v>0.81081081081081086</v>
       </c>
@@ -13291,16 +13002,16 @@
       <c r="A16" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="15">
         <v>515</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="15">
         <v>15</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="15">
         <v>11</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="16">
         <f t="shared" si="0"/>
         <v>0.73333333333333328</v>
       </c>
@@ -13316,16 +13027,16 @@
       <c r="A17" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="15">
         <v>516</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="15">
         <v>12</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="15">
         <v>9</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="16">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -13341,16 +13052,16 @@
       <c r="A18" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="15">
         <v>516</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="15">
         <v>35</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="15">
         <v>22</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="16">
         <f t="shared" si="0"/>
         <v>0.62857142857142856</v>
       </c>
@@ -13366,16 +13077,16 @@
       <c r="A19" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="15">
         <v>517</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="15">
         <v>20</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="15">
         <v>12</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="16">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
@@ -13404,16 +13115,16 @@
       <c r="A21" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="15">
         <v>518</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="15">
         <v>16</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="15">
         <v>12</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="16">
         <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;""),D21/C21,"")</f>
         <v>0.75</v>
       </c>
@@ -13429,16 +13140,16 @@
       <c r="A22" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="15">
         <v>518</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="15">
         <v>33</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="15">
         <v>25</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="16">
         <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;""),D22/C22,"")</f>
         <v>0.75757575757575757</v>
       </c>
@@ -13454,12 +13165,12 @@
       <c r="A23" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="15">
         <v>519</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23" t="str">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16" t="str">
         <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;""),D23/C23,"")</f>
         <v/>
       </c>
@@ -13475,16 +13186,16 @@
       <c r="A24" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="15">
         <v>520</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="15">
         <v>6</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="15">
         <v>6</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="16">
         <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;""),D24/C24,"")</f>
         <v>1</v>
       </c>
@@ -13513,16 +13224,16 @@
       <c r="A26" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="15">
         <v>521</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="15">
         <v>24</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="15">
         <v>15</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="16">
         <f t="shared" ref="E26:E32" si="2">IF(AND(C26&lt;&gt;"",D26&lt;&gt;""),D26/C26,"")</f>
         <v>0.625</v>
       </c>
@@ -13538,16 +13249,16 @@
       <c r="A27" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="15">
         <v>521</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="15">
         <v>11</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="15">
         <v>8</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="16">
         <f t="shared" si="2"/>
         <v>0.72727272727272729</v>
       </c>
@@ -13563,16 +13274,16 @@
       <c r="A28" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="15">
         <v>522</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="15">
         <v>18</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="15">
         <v>12</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="16">
         <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
@@ -13588,16 +13299,16 @@
       <c r="A29" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="15">
         <v>523</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="15">
         <v>27</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="15">
         <v>22</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="16">
         <f t="shared" si="2"/>
         <v>0.81481481481481477</v>
       </c>
@@ -13613,16 +13324,16 @@
       <c r="A30" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="15">
         <v>524</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="15">
         <v>13</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="15">
         <v>7</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="16">
         <f t="shared" si="2"/>
         <v>0.53846153846153844</v>
       </c>
@@ -13638,16 +13349,16 @@
       <c r="A31" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="15">
         <v>525</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="15">
         <v>33</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="15">
         <v>31</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="16">
         <f t="shared" si="2"/>
         <v>0.93939393939393945</v>
       </c>
@@ -13663,16 +13374,16 @@
       <c r="A32" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="15">
         <v>525</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="15">
         <v>12</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="15">
         <v>10</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="16">
         <f t="shared" si="2"/>
         <v>0.83333333333333337</v>
       </c>
@@ -13701,16 +13412,16 @@
       <c r="A34" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="15">
         <v>526</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="15">
         <v>25</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="15">
         <v>20</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="16">
         <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;""),D34/C34,"")</f>
         <v>0.8</v>
       </c>
@@ -13726,16 +13437,16 @@
       <c r="A35" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="15">
         <v>526</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="15">
         <v>20</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="15">
         <v>16</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="16">
         <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;""),D35/C35,"")</f>
         <v>0.8</v>
       </c>
@@ -13764,16 +13475,16 @@
       <c r="A37" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="15">
         <v>526</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="15">
         <v>4</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="15">
         <v>4</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="16">
         <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;""),D37/C37,"")</f>
         <v>1</v>
       </c>
@@ -13789,16 +13500,16 @@
       <c r="A38" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="15">
         <v>527</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="15">
         <v>17</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="15">
         <v>10</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="16">
         <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;""),D38/C38,"")</f>
         <v>0.58823529411764708</v>
       </c>
@@ -13814,16 +13525,16 @@
       <c r="A39" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="15">
         <v>528</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="15">
         <v>55</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="15">
         <v>33</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="16">
         <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;""),D39/C39,"")</f>
         <v>0.6</v>
       </c>
@@ -14270,207 +13981,207 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="158" priority="100" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="E6:E8">
+    <cfRule type="cellIs" dxfId="146" priority="22" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="101" operator="between">
+    <cfRule type="cellIs" dxfId="145" priority="23" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="144" priority="24" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:E12">
+    <cfRule type="cellIs" dxfId="143" priority="19" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="20" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="21" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:E19">
+    <cfRule type="cellIs" dxfId="140" priority="16" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="17" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="18" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E24">
+    <cfRule type="cellIs" dxfId="137" priority="10" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="11" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="12" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:E32">
+    <cfRule type="cellIs" dxfId="134" priority="7" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="8" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="9" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34:E35">
+    <cfRule type="cellIs" dxfId="131" priority="4" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="5" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="6" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:E39">
+    <cfRule type="cellIs" dxfId="128" priority="2" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="3" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="1" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E40">
+    <cfRule type="cellIs" dxfId="125" priority="100" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="101" operator="between">
+      <formula>0.8</formula>
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="155" priority="114" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="113" operator="between">
+    <cfRule type="cellIs" dxfId="122" priority="112" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="113" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="112" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
+    <cfRule type="cellIs" dxfId="120" priority="114" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I8">
-    <cfRule type="cellIs" dxfId="152" priority="115" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="119" priority="115" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="116" operator="between">
+    <cfRule type="cellIs" dxfId="118" priority="116" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="117" operator="lessThan">
+    <cfRule type="cellIs" dxfId="117" priority="117" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I12">
-    <cfRule type="cellIs" dxfId="149" priority="124" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="116" priority="124" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="125" operator="between">
+    <cfRule type="cellIs" dxfId="115" priority="125" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="126" operator="lessThan">
+    <cfRule type="cellIs" dxfId="114" priority="126" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I19">
-    <cfRule type="cellIs" dxfId="146" priority="133" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="133" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="134" operator="between">
+    <cfRule type="cellIs" dxfId="112" priority="134" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="135" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="135" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I24">
-    <cfRule type="cellIs" dxfId="143" priority="151" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="110" priority="151" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="152" operator="between">
+    <cfRule type="cellIs" dxfId="109" priority="152" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I32">
-    <cfRule type="cellIs" dxfId="140" priority="163" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="107" priority="163" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="164" operator="between">
+    <cfRule type="cellIs" dxfId="106" priority="164" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="105" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I35">
-    <cfRule type="cellIs" dxfId="137" priority="184" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="104" priority="184" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="185" operator="between">
+    <cfRule type="cellIs" dxfId="103" priority="185" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="186" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="186" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37:I40">
-    <cfRule type="cellIs" dxfId="134" priority="190" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="101" priority="190" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="191" operator="between">
+    <cfRule type="cellIs" dxfId="100" priority="191" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="192" operator="lessThan">
+    <cfRule type="cellIs" dxfId="99" priority="192" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42">
-    <cfRule type="cellIs" dxfId="131" priority="204" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="202" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="98" priority="202" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="203" operator="between">
+    <cfRule type="cellIs" dxfId="97" priority="203" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E8">
-    <cfRule type="cellIs" dxfId="23" priority="22" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="23" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="24" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10:E12">
-    <cfRule type="cellIs" dxfId="20" priority="19" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="21" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:E19">
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E24">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E32">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E34:E35">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E37:E39">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>0.8</formula>
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="96" priority="204" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14495,20 +14206,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="22" t="s">
         <v>98</v>
       </c>
       <c r="B3" s="18"/>
@@ -14516,7 +14227,7 @@
       <c r="D3" s="18"/>
       <c r="E3" s="19"/>
       <c r="F3" s="13"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="17" t="s">
         <v>99</v>
       </c>
       <c r="H3" s="18"/>
@@ -15749,219 +15460,219 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="125" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="92" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="91" priority="8" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="90" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E16">
-    <cfRule type="cellIs" dxfId="122" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="89" priority="16" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="88" priority="17" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:E19">
-    <cfRule type="cellIs" dxfId="119" priority="28" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="86" priority="28" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="29" operator="between">
+    <cfRule type="cellIs" dxfId="85" priority="29" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="84" priority="30" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E25">
-    <cfRule type="cellIs" dxfId="116" priority="34" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="83" priority="34" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="35" operator="between">
+    <cfRule type="cellIs" dxfId="82" priority="35" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="36" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27:E30">
-    <cfRule type="cellIs" dxfId="113" priority="49" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="80" priority="49" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="50" operator="between">
+    <cfRule type="cellIs" dxfId="79" priority="50" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="51" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="51" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E36">
-    <cfRule type="cellIs" dxfId="110" priority="61" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="77" priority="61" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="62" operator="between">
+    <cfRule type="cellIs" dxfId="76" priority="62" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="75" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E45">
-    <cfRule type="cellIs" dxfId="107" priority="77" operator="between">
+    <cfRule type="cellIs" dxfId="74" priority="76" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="77" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="78" operator="lessThan">
+    <cfRule type="cellIs" dxfId="72" priority="78" operator="lessThan">
       <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="76" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="104" priority="100" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="71" priority="100" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="101" operator="between">
+    <cfRule type="cellIs" dxfId="70" priority="101" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="102" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="102" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="101" priority="103" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="68" priority="103" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="104" operator="between">
+    <cfRule type="cellIs" dxfId="67" priority="104" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="105" operator="lessThan">
+    <cfRule type="cellIs" dxfId="66" priority="105" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="98" priority="111" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="109" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="65" priority="109" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="110" operator="between">
+    <cfRule type="cellIs" dxfId="64" priority="110" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="111" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="95" priority="118" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="118" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="119" operator="between">
+    <cfRule type="cellIs" dxfId="61" priority="119" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="120" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="120" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="92" priority="130" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="59" priority="130" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="131" operator="between">
+    <cfRule type="cellIs" dxfId="58" priority="131" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="57" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I25">
-    <cfRule type="cellIs" dxfId="89" priority="136" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="56" priority="136" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="137" operator="between">
+    <cfRule type="cellIs" dxfId="55" priority="137" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="138" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="138" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I30">
-    <cfRule type="cellIs" dxfId="86" priority="151" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="53" priority="151" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="152" operator="between">
+    <cfRule type="cellIs" dxfId="52" priority="152" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32:I36">
-    <cfRule type="cellIs" dxfId="83" priority="163" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="50" priority="163" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="164" operator="between">
+    <cfRule type="cellIs" dxfId="49" priority="164" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="165" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="165" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38:I45">
-    <cfRule type="cellIs" dxfId="80" priority="179" operator="between">
+    <cfRule type="cellIs" dxfId="47" priority="178" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="179" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="178" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="180" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47">
-    <cfRule type="cellIs" dxfId="77" priority="204" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="202" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="44" priority="202" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="203" operator="between">
+    <cfRule type="cellIs" dxfId="43" priority="203" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="204" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15985,20 +15696,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="22" t="s">
         <v>98</v>
       </c>
       <c r="B3" s="18"/>
@@ -16006,7 +15717,7 @@
       <c r="D3" s="18"/>
       <c r="E3" s="19"/>
       <c r="F3" s="13"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="17" t="s">
         <v>99</v>
       </c>
       <c r="H3" s="18"/>
@@ -17085,171 +16796,171 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" dxfId="74" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E11">
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="38" priority="7" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="37" priority="8" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="9" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13:E20">
-    <cfRule type="cellIs" dxfId="68" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="35" priority="16" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="34" priority="17" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="18" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="65" priority="40" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="40" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="41" operator="between">
+    <cfRule type="cellIs" dxfId="31" priority="41" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="42" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:E32">
-    <cfRule type="cellIs" dxfId="62" priority="62" operator="between">
+    <cfRule type="cellIs" dxfId="29" priority="61" operator="greaterThanOrEqual">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="62" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="61" operator="greaterThanOrEqual">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="63" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="63" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:E39">
-    <cfRule type="cellIs" dxfId="59" priority="72" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="70" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="26" priority="70" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="71" operator="between">
+    <cfRule type="cellIs" dxfId="25" priority="71" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="72" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="56" priority="90" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="88" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="88" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="89" operator="between">
+    <cfRule type="cellIs" dxfId="22" priority="89" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="90" operator="lessThan">
+      <formula>0.8</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:I7">
-    <cfRule type="cellIs" dxfId="53" priority="91" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="91" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="92" operator="between">
+    <cfRule type="cellIs" dxfId="19" priority="92" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="93" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I11">
-    <cfRule type="cellIs" dxfId="50" priority="97" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="97" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="98" operator="between">
+    <cfRule type="cellIs" dxfId="16" priority="98" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="99" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="99" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I20">
-    <cfRule type="cellIs" dxfId="47" priority="106" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="106" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="107" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="107" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="108" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="108" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I28">
-    <cfRule type="cellIs" dxfId="44" priority="130" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="130" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="131" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="131" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="132" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="132" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I32">
-    <cfRule type="cellIs" dxfId="41" priority="151" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="151" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="152" operator="between">
+    <cfRule type="cellIs" dxfId="7" priority="152" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="153" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="153" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:I39">
-    <cfRule type="cellIs" dxfId="38" priority="160" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="160" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="161" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="161" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="162" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="162" operator="lessThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41">
-    <cfRule type="cellIs" dxfId="35" priority="180" operator="lessThan">
-      <formula>0.8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="178" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="178" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="179" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="179" operator="between">
       <formula>0.8</formula>
       <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="180" operator="lessThan">
+      <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
